--- a/Phase6.2/quantized (Cleaned)/load_21.xlsx
+++ b/Phase6.2/quantized (Cleaned)/load_21.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8720"/>
+    <workbookView windowWidth="18350" windowHeight="8720"/>
   </bookViews>
   <sheets>
     <sheet name="Timestamp logs" sheetId="1" r:id="rId1"/>
@@ -34,14 +34,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -497,28 +490,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -527,118 +523,115 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -703,6 +696,9402 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Sensing Unit Program: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.0588592130760805"/>
+          <c:y val="0.172453703703704"/>
+          <c:w val="0.936085601145842"/>
+          <c:h val="0.583425925925926"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$A$1:$A$498</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="498"/>
+                <c:pt idx="0">
+                  <c:v>21.8119</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.4685</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.0692</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.4504</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>13.3889</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>14.6709</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>14.0013</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11.6473</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14.1498</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11.7653</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11.4086</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13.6719</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>11.4181</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>19.4679</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15.0491</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>12.103</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>13.1517</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>14.9083</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>26.1378</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>12.9143</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>17.5552</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>17.7983</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>26.5134</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>35.6633</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>32.2491</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>25.3728</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>28.0052</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>31.4754</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>37.7198</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>31.9259</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>33.1613</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>31.6276</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>29.5412</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>28.9652</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>31.3175</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>22.8796</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>30.8001</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>17.3689</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>22.7392</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>20.6242</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>27.5059</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>33.4327</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>30.3932</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>21.9205</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>30.021</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>27.7047</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>27.5564</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>23.4693</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>27.0877</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>35.4753</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>28.348</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>42.2389</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>37.1519</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>35.7116</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>19.4205</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>26.9717</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>33.9091</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>29.1618</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>32.1237</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>29.6408</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>36.8433</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>31.2868</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>24.7205</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>37.7298</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>17.2668</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>26.3409</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>43.9641</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>19.0962</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>28.8343</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>27.049</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>29.3904</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>29.4465</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>32.2904</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>29.7985</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>29.2679</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>22.7435</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>19.3739</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>28.5185</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>30.151</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>38.3259</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>40.6826</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>25.0144</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>25.401</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>29.8428</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>35.2188</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>30.2253</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>32.6939</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>24.6464</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>34.7252</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>28.4464</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>42.0937</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>27.8717</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>20.9251</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>33.4247</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>26.9374</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>31.7408</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>40.5495</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>23.5104</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>39.0357</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>70.4143</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>33.3797</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>24.9016</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>27.572</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>30.1825</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>38.9765</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>28.0662</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>21.8763</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>18.6974</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>14.5775</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>11.5064</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>16.046</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>18.465</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>12.6335</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>14.0317</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>17.7981</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>12.0464</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>16.8556</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>14.2596</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>28.3367</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>16.8033</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>11.4528</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>10.5269</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>16.6796</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>16.0034</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>12.975</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>12.5017</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>21.3863</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>18.7902</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>14.9309</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>10.7377</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>10.9423</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>10.3339</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>11.0592</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>11.8407</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>13.5126</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>16.5768</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>13.7484</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>11.9757</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>12.6011</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>14.327</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>12.5545</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>16.9043</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>18.886</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>12.157</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>12.4664</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>12.3962</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>11.7161</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>12.0188</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>21.7153</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>15.0948</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>17.6417</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>16.0548</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>18.392</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>18.9656</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>13.9099</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>10.9254</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>12.7741</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>12.4929</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>12.254</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>13.0784</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>11.7383</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>12.0297</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>11.1496</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>15.49</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>9.7145</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>13.0927</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>10.946</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>17.5985</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>11.0113</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>11.5647</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>15.9704</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>20.0337</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>12.5004</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>18.8533</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>12.5782</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>13.0873</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>22.6697</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>27.7634</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>20.0511</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>10.1719</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>18.2733</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>11.812</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>118.7586</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>12.8987</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>13.5886</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>10.5386</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>11.9332</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>14.1053</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>11.9581</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>11.2712</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>11.7434</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>20.3058</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>14.8811</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>12.0561</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>10.4685</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>19.878</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>23.9637</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>17.6188</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>12.4946</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>18.9855</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>20.0969</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>16.8415</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>11.3882</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>10.5186</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>19.6506</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>11.9126</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>9.6466</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>11.652</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>16.2009</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>13.5792</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>12.8417</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>12.8609</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>16.9717</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>15.9262</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>12.1659</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>15.6997</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>11.3417</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>17.0923</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>11.0143</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>18.3101</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>11.5221</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>14.2423</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>11.4867</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>18.9773</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>13.1007</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>13.6883</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>14.6756</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>16.4951</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>11.2971</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>12.7101</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>18.9872</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>14.5826</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>12.5142</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>11.7568</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>19.0857</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>10.8575</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>12.023</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>30.4033</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>22.9602</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>15.5377</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>12.0464</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>17.9913</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>17.0706</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>10.4699</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>19.0888</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>18.1913</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>15.7561</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>17.822</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>12.5778</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>19.6465</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>17.2663</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>16.8689</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>13.6126</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>15.475</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>12.6301</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>13.2341</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>13.4783</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>15.6812</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>14.256</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>14.3278</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>10.9662</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>18.2498</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>10.9208</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>14.3692</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>13.515</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>9.3662</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>10.9406</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>11.1133</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>14.0375</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>16.1307</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>17.9951</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>11.7781</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>20.8904</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>14.0731</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>13.1687</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>9.8625</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>14.6703</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>11.6576</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>13.8302</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>10.3237</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>10.9839</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>9.7131</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>14.3812</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>13.2061</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>16.6042</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>17.8148</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>13.8295</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>10.5319</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>19.2912</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>13.2378</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>10.6412</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>16.6575</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>12.8228</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>15.8807</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>11.9377</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>18.0267</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>12.4983</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>17.6983</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>17.3942</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>11.2551</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>17.495</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>14.5167</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>11.5155</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>14.1847</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>10.9064</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>11.8825</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>14.9559</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>12.2655</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>12.4535</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>14.377</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>12.6645</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>18.5678</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>12.2576</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>16.1769</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>14.9539</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>12.3977</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>116.5191</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>18.2208</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>12.015</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>10.6552</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>14.5759</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>11.0905</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>16.6727</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>15.2765</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>13.1855</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>17.1192</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>17.8248</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>17.4691</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>18.1884</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>25.8203</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>13.8524</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>12.5483</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>25.3356</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>19.409</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>18.4626</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>14.9677</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>16.3859</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>17.2268</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>11.3423</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>11.3821</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>14.1449</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>20.041</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>14.941</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>12.8426</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>19.4059</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>16.3711</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>10.2567</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>10.7969</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>22.7137</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>12.6901</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>118.9964</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>13.4049</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>13.8376</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>10.1583</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>12.4932</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>11.2894</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>14.772</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>12.3646</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>16.5888</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>13.1151</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>13.958</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>11.978</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>13.782</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>16.5591</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>15.9759</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>17.2828</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>11.3149</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>15.013</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>13.8519</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>11.9832</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>18.2385</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>16.9254</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>14.2136</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>16.3744</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>19.4065</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>15.8532</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>20.9444</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>16.0739</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>19.8994</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>19.2556</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>10.8224</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>10.9257</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>13.9335</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>13.1316</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>13.1912</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>13.6293</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>24.5558</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>15.8002</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>11.742</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>10.4396</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>10.2644</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>14.4215</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>11.4501</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>18.9487</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>22.0018</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>15.0707</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>12.888</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>11.1542</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>9.8423</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>10.2553</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>10.7985</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>10.2615</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>19.8737</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>28.47</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>15.5585</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>20.2845</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>10.4847</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>22.2626</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>14.6453</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>12.4065</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>11.021</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>15.055</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>13.2322</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>18.2816</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>14.0645</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>16.8618</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>18.3312</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>20.3438</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>15.2424</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>15.23</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>16.2071</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>17.0511</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>10.9195</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>15.2266</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>9.9131</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>13.2482</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>10.7035</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>12.181</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>17.0244</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>12.6292</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>12.27</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>13.3696</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>11.5973</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>12.4828</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>17.9018</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>18.3671</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>14.8256</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>18.3035</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>14.8162</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>21.7242</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>10.4954</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>13.31</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>20.678</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>15.1759</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>11.7036</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>11.4671</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>20.4597</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>12.3833</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>11.6398</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>13.9681</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>13.4059</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>11.5665</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>10.9941</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>14.427</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>10.9738</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>12.0675</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>15.9399</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>14.1206</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>16.129</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>27.918</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>10.4659</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>10.7444</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>12.2965</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>23.6107</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>13.018</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>18.3187</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>11.4097</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>11.5439</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>23.8183</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>10.4425</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>13.7522</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>11.0184</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>13.6662</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>14.7381</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>11.5374</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>9.6565</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>12.0728</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>9.6505</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>12.2157</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>19.0492</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>10.8436</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>11.6476</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>14.5188</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>12.3435</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>13.3508</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>10.9824</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>12.2872</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>10.9151</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>12.5418</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>9.8876</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>13.761</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>15.9147</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>12.9261</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>24.1903</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>10.9872</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>13.6201</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>18.0482</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>11.8877</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="88038310"/>
+        <c:axId val="389297112"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="88038310"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="389297112"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="389297112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="88038310"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Queue Lifetime: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$B$1:$B$498</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="498"/>
+                <c:pt idx="0">
+                  <c:v>337.087882</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>390.592649</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1075.03873</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1078.433167</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1565.3661</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1820.573705</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2528.19928</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2581.645378</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2898.88872</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3354.003749</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3665.307976</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4073.653231</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4136.802218</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4616.416455</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4924.356655</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5078.486798</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5540.03501</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5645.062426</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5991.879634</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>6057.03174</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6585.489412</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5824.394987</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6513.472116</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6108.441002</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6435.347387</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>6216.469779</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>6390.594355</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>6655.524747</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6286.980684</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>6747.77097</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6329.643723</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>7053.577369</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>6545.896608</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>6929.239638</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>6906.642716</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>6950.215861</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7017.95362</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>7077.238178</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>7362.595996</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>7103.034724</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>7507.076263</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>6988.050911</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>7455.542089</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>7242.345772</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>7397.817035</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>7362.021162</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>7332.020943</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>7356.751053</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>7039.701351</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>7110.322606</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>6781.112378</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>6707.063158</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>6108.713617</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>6520.7847</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>6446.060344</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>6535.050668</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>6919.687833</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>6637.218131</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>6899.097628</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>6553.307755</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>7118.000342</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>6796.860596</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>6841.882951</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>6679.925233</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>6573.830583</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>6768.500089</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>6679.371413</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>6963.238933</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>6972.530801</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>7088.187703</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>7374.257209</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>7219.835823</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>7058.312083</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>7091.615724</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>6605.529616</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>6751.62519</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>6677.296562</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>6776.792106</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>6621.347212</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>6508.336702</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>6732.376518</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>6383.432719</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>6835.409283</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>6256.434785</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>6588.161958</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>6439.165015</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>6386.211534</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>6824.056647</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>6718.000524</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>6526.764952</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>7015.928031</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>6665.50637</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>6947.915784</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>6724.57</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>6644.983784</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>6666.80605</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>6542.913248</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>6902.310766</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>6320.180977</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>6973.527741</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>6683.379871</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>7152.609747</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>7131.505553</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>6842.0352</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>7095.251913</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>6233.921084</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>6459.751288</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>6234.413725</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>6261.367488</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>6160.848097</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>6166.993071</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>6257.49788</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>6105.591879</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>6612.970319</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>6189.588869</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>6173.786912</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>6442.834483</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>5973.555851</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>6075.51455</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>5757.147287</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>5729.178798</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>5637.997439</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>5695.295883</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>6147.789952</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>5573.280847</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>6147.540894</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>5626.998145</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>5927.094065</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>5963.623132</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>5934.699332</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>6054.56331</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>5407.84644</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>5859.800866</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>5480.277216</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>5667.071631</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>5520.915573</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>5472.50494</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>5781.330282</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>5364.290348</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>5645.554753</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>5278.274982</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>5112.398455</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>5170.187667</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>4945.941293</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>5100.201103</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>5069.894118</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>4907.25098</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>4950.830522</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>4687.555156</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>5149.361071</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>4814.596668</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>5131.708965</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>4886.875856</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>4756.712962</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>4643.476901</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>4604.571107</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>4615.643653</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>4540.752877</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>4745.26264</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>4560.862676</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>4891.674281</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>4631.542449</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>4744.000146</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>4677.29713</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>4365.582538</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>4563.739881</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>4723.369083</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>4194.834379</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>4295.61241</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>4173.574739</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>4218.034465</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>4170.462948</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>4248.613892</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>3945.620813</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>3846.902284</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>3920.693245</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>3644.459788</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>3613.856202</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>3486.56051</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>3728.289837</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>3379.476162</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>3452.323812</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>3396.267915</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>3425.798395</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>3294.80894</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>3361.2754</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>3326.032305</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>3412.509723</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>3346.885026</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>3382.125833</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>3517.952197</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>3472.760824</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>3475.234926</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>3583.168666</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>3807.148101</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>3668.205533</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>3833.213875</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>3740.550745</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>3981.479808</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>3661.279305</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>3873.88842</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>3794.920758</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>3579.34014</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>3851.481971</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>3747.306691</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>3485.279108</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>3824.742211</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>3847.828771</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>3832.087616</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>3845.6403</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>3782.865541</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>3914.844598</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>3698.769226</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>3843.624955</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>3724.771775</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>3796.055742</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>3755.69912</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>3795.98559</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>4069.485954</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>3982.86558</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>4031.615861</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>3946.812338</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>4013.913762</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>4242.585941</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>3832.339625</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>3979.679933</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>3737.197173</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>3928.81519</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>4116.722584</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>3844.207223</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>3920.151715</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>4367.329277</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>4143.62019</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>3868.635899</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>4369.819508</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>4323.912206</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>3846.523766</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>4112.45931</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>4166.595732</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>4324.147581</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>4319.039938</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>4192.095984</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>4292.138892</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>4214.897322</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>4547.741669</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>4310.895172</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>4232.689577</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>4638.038511</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>4538.723324</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>4388.670518</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>4492.069119</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>4510.698698</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>4138.064169</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>4338.652236</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>4331.63324</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>4650.246515</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>4717.565816</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>4636.16793</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>4441.077152</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>4404.343928</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>4456.74521</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>4581.201803</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>4203.440385</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>4332.203014</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>4445.794741</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>4160.172861</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>4176.047972</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>4027.930755</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>4263.500471</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>4307.965304</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>4153.500442</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>4256.544921</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>4449.366395</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>3839.888006</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>3843.314711</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>3905.015522</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>3992.055021</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>3846.493217</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>4006.418147</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>3868.193693</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>3817.771619</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>4402.111192</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>4151.524496</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>3745.66907</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>4235.123705</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>4041.61526</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>3626.581789</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>3989.985088</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>3866.07451</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>3729.2103</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>3914.238171</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>3882.311081</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>4037.739954</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>3862.961615</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>4165.656975</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>4137.806638</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>3737.56491</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>4080.447605</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>4073.106685</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>3710.446672</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>3823.397623</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>3845.087265</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>3610.913574</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>3982.002408</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>4083.300174</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>3843.07978</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>3966.571435</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>3876.099744</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>3712.543926</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>3793.181164</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>3805.343799</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>3968.250064</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>3661.983294</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>3748.589787</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>4034.627478</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>3760.988867</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>3977.148393</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>3825.776042</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>3837.304104</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>4258.111695</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>4169.913332</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>3832.12249</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>4365.181351</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>4296.736842</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>4168.26454</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>4637.400674</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>4542.388741</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>4436.077128</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>4472.373375</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>4236.69188</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>4358.896706</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>4388.043131</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>4283.111504</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>4250.907248</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>3930.587417</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>3976.870599</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>4371.884456</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>3860.358639</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>3795.743844</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>4244.15169</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>3654.676992</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>4069.503332</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>4066.210313</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>3635.002039</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>3829.864851</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>3946.111735</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>3563.290412</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>3776.458869</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>3781.97778</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>4051.101206</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>3687.637386</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>3686.342898</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>3961.433608</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>3963.614421</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>3982.264021</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>4081.942043</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>4123.037898</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>3867.082732</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>3945.507045</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>3700.611921</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>3835.116127</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>3972.165111</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>3772.588608</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>3690.121025</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>4154.317578</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>3947.225432</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>3864.445082</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>3792.907937</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>3931.995986</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>3944.90393</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>4169.118823</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>4125.769045</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>3666.337478</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>3927.510837</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>4173.70111</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>3934.344767</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>3990.442707</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>3929.186448</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>4006.588413</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>3927.040455</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>3936.392589</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>3866.971049</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>3558.882737</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>3718.333414</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>3859.351299</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>3439.784349</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>3701.446609</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>3768.759482</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>3430.42574</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>3564.102902</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>3677.422686</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>3584.74346</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>3509.463246</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>3483.599017</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>3726.472282</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>3701.989734</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>3629.056247</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>3897.89326</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>3747.90901</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>3942.086809</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>3976.584435</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>4123.108516</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>4004.981076</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>4089.058142</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>4138.992095</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>4072.657299</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>3984.097403</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>4488.605765</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>4464.730515</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>4106.713298</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>4361.19942</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>4648.684269</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>4227.207282</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>4158.494348</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>4674.592961</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>4232.085399</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>4375.469604</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>4513.865169</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>4358.139631</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>4331.552786</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>4240.442461</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>4407.499384</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>4244.184007</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>4212.724428</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>4459.095908</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>3869.659947</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>3857.030338</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>4257.21482</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>4065.963885</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>3852.679389</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>3871.653898</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>4025.807607</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>4272.515156</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>4326.700882</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>4153.651814</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>4166.294274</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>4430.944805</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>4437.45711</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>4417.166858</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>4365.318721</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>4373.415063</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>4563.102149</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>4439.072261</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>4589.301091</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>4867.927221</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>4534.716002</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>4499.971005</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>4734.866036</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>4856.9339</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>4774.0826</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>4243.992215</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>4467.891906</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>4446.144834</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>4450.269889</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>4480.998898</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>4165.052997</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>4594.389167</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>4397.259405</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>4296.85104</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>4395.957948</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>4106.478684</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>4246.722698</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>3983.063651</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>4285.979321</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>4132.061802</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>3884.994193</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>4255.744889</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>4161.659559</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>3968.505912</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>4155.180746</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>4543.219879</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>4260.689705</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>4065.480211</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>4253.972629</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>4118.724026</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>4334.650841</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>4455.505901</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>4425.303096</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>4722.473026</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>4553.403805</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>4723.972345</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>4600.064924</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>4779.028872</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>4846.714742</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>4809.365754</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>4844.485095</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>4956.2446</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>5255.045164</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>4859.695527</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>4855.968015</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>5285.211056</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>5163.351142</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>5071.623621</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>5291.347635</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>5222.611719</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>4869.608935</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>5189.87046</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>5023.853322</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="940974691"/>
+        <c:axId val="674594337"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="940974691"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="674594337"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="674594337"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="940974691"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Inference Program: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$C$1:$C$498</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="498"/>
+                <c:pt idx="0">
+                  <c:v>793.346786</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>701.941361</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>792.593239</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>500.873816</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>997.122082</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>750.132815</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>402.730707</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>801.640228</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>773.032557</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>702.856606</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>473.890957</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>904.758654</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>498.310428</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>494.689344</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>647.131773</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>572.561907</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>495.411401</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>500.176715</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>704.075318</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>572.745773</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>700.155935</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>797.347188</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>699.417349</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1100.433085</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>699.166647</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>796.426327</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>703.594778</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>853.716301</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>793.829516</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>749.103928</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>801.903246</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>808.824701</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>700.318789</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>698.038812</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>792.652297</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>597.087729</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>798.160165</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>699.746264</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>792.184114</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>602.209361</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>701.789062</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>994.895389</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1042.754787</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>800.840538</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>746.306476</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>695.783227</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>704.243467</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>399.645401</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>670.879651</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>397.667837</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1056.881761</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>34630.327962</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>501.643819</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>794.843168</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1191.875688</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>802.520309</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>695.784845</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>700.268467</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>802.886797</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>946.562176</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>700.0409</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>949.782467</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>499.070191</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>896.555942</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>764.84029</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>700.984092</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>806.786181</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>703.237555</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>843.437632</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>768.154216</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>745.900414</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>607.115534</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>697.60342</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>533.722225</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>707.553167</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>693.778646</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>750.247447</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>698.549269</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>901.536799</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>698.709234</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>602.566199</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>655.953652</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>595.203417</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>844.556431</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>604.249034</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>1106.955141</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>1192.398906</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>490.089244</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>966.770529</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>750.28837</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>600.52705</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>646.086739</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>498.39415</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>648.369658</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>696.813569</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>947.461701</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>599.448364</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>1098.202864</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>799.172006</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>702.016057</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>1008.965472</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>500.649604</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>589.384829</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>502.557342</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>598.534144</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>527.576235</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>600.265042</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>604.296876</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>700.971786</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>592.915695</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>404.295533</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>1001.397397</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>793.050717</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>898.569411</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>496.461278</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>672.039686</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>605.996381</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>500.261887</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>694.55246</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>471.371325</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>529.73457</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>997.423527</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>499.077185</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>696.953494</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>571.205214</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>404.705734</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>952.11673</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>598.161499</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>498.303496</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>550.988598</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>596.671837</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>549.797384</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>603.153372</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>645.375576</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>429.755942</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>802.625267</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>569.786952</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>352.766704</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>430.181034</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>451.113612</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>397.123914</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>701.440249</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>367.633116</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>526.293616</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>696.956068</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>509.431288</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>301.903005</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>791.23052</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>696.325442</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>496.952191</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>649.553343</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>570.285834</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>700.210532</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>797.028178</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>724.724436</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>650.079009</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>1097.671326</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>502.461433</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>651.150347</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>870.589599</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>803.039941</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>550.083465</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>505.116565</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>750.455039</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>698.851895</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>603.209466</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>549.610255</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>748.874127</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>603.4293</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>644.16249</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>456.913999</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>493.364626</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>402.663931</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>496.290142</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>397.554036</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>399.957763</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>672.279238</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>504.41816</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>647.919974</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>598.305564</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>405.79232</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>706.029297</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>427.133928</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>600.875548</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>700.181264</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>703.593244</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>643.309452</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>669.489788</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>653.450055</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>550.330383</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>529.194302</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>697.604993</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>697.500744</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>667.440792</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>551.805212</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>843.141361</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>523.537098</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>594.312171</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>477.624284</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>501.149977</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>502.221902</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>562.695428</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>599.38835</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>1206.658275</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>593.236939</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>598.684347</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>646.288906</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>496.329761</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>693.122243</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>798.120135</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>595.5256</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>750.123793</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>396.440364</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>699.495281</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>601.686014</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>1054.535831</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>604.046439</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>597.578052</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>429.793042</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>599.34158</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>795.81257</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>673.092455</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>698.666362</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>493.95243</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>696.870306</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>698.157715</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>801.933611</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>623.411755</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>959.124023</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>748.336748</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>506.058965</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>704.792183</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>796.296704</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>749.456618</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>500.241801</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>1210.212044</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>542.501227</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>498.053176</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>806.907306</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>631.430184</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>588.67675</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>859.96379</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>801.790644</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>546.500719</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>895.820683</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>1204.013671</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>631.295721</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>528.654973</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>601.662674</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>543.039414</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>599.614717</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>540.19351</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>1199.0797</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>727.486801</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>1201.335736</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>502.170523</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>552.4233</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>803.689983</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>428.339795</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>696.449927</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>503.406308</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>455.697595</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>849.827958</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>628.876588</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>699.138672</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>699.57967</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>703.807095</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>700.946436</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>595.222814</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>697.978052</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>692.967616</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>502.460137</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>697.188424</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>642.921046</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>529.853838</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>600.876448</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>657.827693</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>674.456303</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>897.610008</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>798.583014</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>691.482685</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>646.829355</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>603.279821</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>593.827263</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>647.98136</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>426.638092</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>502.878482</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>667.199966</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>1000.394295</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>552.585713</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>624.131714</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>951.400297</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>598.882728</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>473.950465</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>655.959813</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>529.506111</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>896.717263</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>599.569951</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>446.965379</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>498.787857</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>696.721146</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>794.785762</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>697.813055</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>546.249862</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>400.35314</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>547.448854</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>501.952611</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>755.472725</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>840.174937</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>702.415718</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>558.731134</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>550.514987</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>726.704063</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>998.613249</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>656.164617</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>570.092426</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>897.080631</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>647.154635</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>700.310582</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>1098.568625</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>803.632067</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>701.686931</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>602.232261</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>756.736301</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>758.838915</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>633.481341</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>501.253046</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>603.571742</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>496.954847</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>857.610088</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>451.282403</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>567.599114</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>399.644199</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>695.39563</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>624.582596</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>597.101816</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>704.338953</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>572.467678</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>1104.906673</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>604.662709</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>595.190426</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>499.110669</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>605.680033</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>598.40652</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>426.913708</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>500.520026</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>1041.356854</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>701.936789</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>600.528833</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>468.406071</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>500.141803</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>1098.002072</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>628.949349</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>745.899067</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>469.593368</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>796.123439</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>454.001832</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>625.913725</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>544.797478</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>600.317139</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>501.325831</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>801.606083</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>649.50731</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>672.078457</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>743.465676</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>545.189539</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>721.66879</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>799.953568</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>805.288532</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>602.669461</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>907.973615</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>497.162078</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>694.110865</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>570.513648</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>499.045522</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>644.065716</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>500.190977</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>595.073113</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>545.8661</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>308.367628</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>440.171713</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>696.165931</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>498.756358</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>658.005654</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>796.743051</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>569.098365</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>596.076184</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>595.852121</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>746.520164</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>741.735018</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>573.844295</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>698.864298</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>762.69308</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>600.391287</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>652.638334</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>569.158596</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>702.891886</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>949.937807</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>499.505164</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>742.802653</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>606.743897</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>698.864433</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>653.61161</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>627.398328</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>1001.646787</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>941.894624</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>700.051614</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>594.894259</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>807.855425</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>854.46226</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>470.65709</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>904.407274</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>701.089883</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>603.424908</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>599.036563</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>600.262704</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>882.54821</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>759.753465</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>434.984364</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>650.35239</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>492.339184</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>802.744107</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>500.177052</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>552.49792</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>597.263488</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>701.217693</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>847.371286</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>504.165951</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>403.317916</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>1206.061885</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>1070.724129</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>957.952539</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>506.080587</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>1196.056998</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>697.201089</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>766.109767</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>695.223104</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>401.523684</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>747.075294</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>797.035096</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>800.300164</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>955.917514</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>599.285318</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>679.207958</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>599.751836</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>794.574093</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>719.822331</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>1004.305018</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>504.545717</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>699.890096</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>642.412603</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>799.34234</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>697.792093</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>853.681404</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>603.688144</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>607.162939</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>551.17927</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>499.999328</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>787.576848</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>505.128265</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>947.34862</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>506.524353</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>488.155737</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>791.439533</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>897.417974</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>600.862809</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>700.447616</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>1094.112873</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>951.408882</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>599.435098</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>504.676441</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>744.28875</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>899.915285</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>703.840309</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>1205.487305</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>504.917636</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>906.808273</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>732.476511</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>741.538707</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>804.207066</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>601.912311</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>901.715993</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>794.31492</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>908.419041</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>1144.174678</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>1096.205078</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>826.1991</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>897.333432</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>996.229522</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>598.640912</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>897.887493</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>801.515385</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>600.333572</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>801.114334</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>796.579185</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>991.599463</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>705.412293</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>1305.953265</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="449079932"/>
+        <c:axId val="273603779"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="449079932"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="273603779"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="273603779"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="449079932"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Entire Pipeline: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$D$1:$D$498</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="498"/>
+                <c:pt idx="0">
+                  <c:v>1152.246568</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1109.00251</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1884.701169</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1590.757383</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2575.877082</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2585.37742</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2944.931287</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3394.932906</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3686.071077</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4068.625655</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4150.607533</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4992.083785</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4646.530746</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5130.573699</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5586.537528</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5663.151705</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>6048.598111</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>6160.147441</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6722.092752</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>6642.691813</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>7303.200547</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6639.540475</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>7239.402865</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>7244.537387</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>7166.763134</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7038.268906</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7122.194333</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>7540.716448</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>7118.53</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>7528.800798</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>7164.708269</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>7894.02967</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>7275.756597</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>7656.24365</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>7730.612513</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>7570.18319</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7846.913885</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>7794.353342</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>8177.51931</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>7725.868285</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>8236.371225</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>8016.379</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>8528.690076</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>8065.10681</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>8174.144511</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>8085.509089</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>8063.82081</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>7779.865754</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>7737.668702</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>7543.465743</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>7866.342139</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>41379.63002</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>6647.509336</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>7351.339468</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>7657.356532</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>7364.542677</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>7649.381778</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>7366.648398</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>7734.108125</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>7529.510731</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>7854.884542</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>7777.929863</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>7365.673642</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>7614.210975</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>7355.937673</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>7495.825081</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>7530.121694</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>7685.572688</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>7844.802733</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>7883.390919</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>8149.548023</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>7856.397857</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>7788.205903</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>7655.136449</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>7342.350683</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>7468.147336</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>7446.917909</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>7503.859875</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>7553.035011</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>7245.371836</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>7375.625317</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>7064.400771</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>7456.0137</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>7130.834016</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>7227.629792</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>7576.345456</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>7611.30434</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>7338.792291</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>7719.496253</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>7305.499722</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>7658.548781</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>7339.464809</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>7467.235034</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>7406.364358</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>7368.734753</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>7646.008551</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>7182.911112</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>8024.02403</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>7158.388683</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>7745.958098</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>7725.725043</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>7678.160951</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>7748.462382</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>7374.775042</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>7732.762557</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>6789.563519</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>7081.89263</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>6857.408001</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>6976.916774</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>6765.270192</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>6587.334604</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>7277.360277</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>6911.276096</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>7525.57143</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>6703.848247</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>6857.872998</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>7065.686464</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>6488.077338</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>6798.40371</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>6245.321912</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>6270.366168</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>6645.947866</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>6211.052668</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>6860.746846</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>6157.461061</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>6564.748328</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>6600.501175</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>6544.045764</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>6476.857528</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>6496.42563</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>6662.177447</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>5967.977724</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>6474.013438</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>6137.493492</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>6110.340173</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>6340.11764</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>6056.040292</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>6146.072686</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>5807.072482</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>6110.995365</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>5687.953396</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>5830.743004</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>5556.706783</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>5484.391909</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>5809.623571</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>5591.721606</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>5220.870085</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>5754.079842</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>5405.595898</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>5661.408062</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>5481.791711</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>5718.049599</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>5605.478388</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>5572.70674</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>5382.111237</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>5265.575516</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>5726.089079</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>5055.70721</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>5408.666987</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>5444.530675</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>5706.452522</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>5193.655614</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>5260.266311</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>5443.242169</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>5074.148933</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>5180.042047</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>5283.925338</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>4961.307006</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>4910.05301</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>4829.301929</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>4690.918864</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>4683.861274</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>4663.778223</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>4460.764255</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>4257.03452</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>4333.738308</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>4339.408726</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>4146.037762</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>4154.531584</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>4336.767301</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>3803.541782</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>4170.165109</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>3942.160443</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>4039.572643</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>4008.578804</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>4075.407244</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>3981.274957</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>4096.104811</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>4012.293181</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>3943.727416</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>4058.889899</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>4190.671617</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>4187.61677</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>4262.665558</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>4369.421813</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>4531.224894</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>4380.714673</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>4352.481716</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>4471.598692</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>4181.414782</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>4396.207222</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>4374.457686</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>4190.11669</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>5068.658846</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>4360.19423</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>4095.876055</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>4480.677717</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>4355.810532</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>4541.410759</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>4657.339635</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>4391.232841</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>4677.829291</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>4112.18129</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>4559.046436</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>4338.623689</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>4866.291273</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>4371.087259</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>4410.655942</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>4510.293296</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>4600.51726</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>4838.950531</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>4634.147093</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>4724.066824</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>4755.515671</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>4542.310631</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>4691.525948</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>4553.806384</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>4568.722045</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>5087.143707</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>4605.254071</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>4445.19788</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>5086.70406</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>4952.431094</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>4629.849317</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>4889.147009</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>5544.98175</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>4401.047993</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>4640.915786</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>4996.463238</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>4971.115465</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>4919.763088</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>5070.051074</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>5111.000136</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>4771.867941</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>5462.651152</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>5533.100143</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>4879.741398</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>5184.515484</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>5152.963798</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>4951.356432</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>5108.950136</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>5067.761108</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>5350.756469</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>5081.614037</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>5545.599076</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>5165.651138</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>5283.467416</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>5455.539113</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>4883.672947</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>5115.121655</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>4971.117718</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>5055.149198</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>5064.189143</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>4975.448802</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>5158.448413</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>4869.118731</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>4890.795667</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>4739.990491</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>4872.760785</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>5022.074056</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>4864.463158</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>4770.783158</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>5167.445219</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>4496.882152</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>4386.337249</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>4515.75447</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>4664.553014</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>4532.60712</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>4917.858355</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>4677.100407</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>4520.238204</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>5058.653647</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>4769.185517</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>4352.702433</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>4899.709265</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>4486.068152</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>4143.289771</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>4667.716954</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>4885.760005</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>4295.033813</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>4549.011085</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>4850.368878</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>4649.445482</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>4352.79278</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>4833.554488</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>4685.339449</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>4646.780473</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>4697.715856</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>4537.466264</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>4220.489629</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>4537.613769</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>4654.389727</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>4320.242129</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>4542.43697</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>4494.559714</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>4402.411134</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>4483.479946</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>4643.837969</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>4565.172363</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>4509.973882</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>4376.739433</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>4537.332851</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>4400.944957</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>4763.379936</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>4705.745995</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>4343.478993</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>4990.748124</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>4491.151477</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>4549.629686</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>5367.33552</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>4988.121299</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>4544.899921</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>4984.086312</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>5068.749643</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>4940.288955</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>5288.001215</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>5061.466587</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>5057.11797</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>4987.516622</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>5120.122268</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>4824.031509</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>4968.190545</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>4708.091303</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>4965.711878</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>4573.632613</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>4588.940115</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>5092.609309</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>4450.053117</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>4911.992817</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>4860.196499</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>4264.012318</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>4588.655001</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>4686.831346</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>4246.251159</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>4276.184459</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>4463.002861</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>4614.903966</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>4489.192558</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>4405.220313</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>4532.197377</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>4306.775589</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>4797.74987</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>4604.220557</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>4719.671788</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>4464.350589</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>4889.354882</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>4591.81173</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>4505.361057</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>4506.893323</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>4314.04416</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>4350.399958</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>4785.749194</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>4435.877918</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>4378.758582</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>4913.759154</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>4509.697771</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>4597.428772</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>4607.874505</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>4751.136418</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>4559.556591</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>5095.330938</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>4639.856523</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>4374.661943</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>4514.398885</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>4692.153132</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>4594.263683</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>4511.578084</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>4540.333461</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>4572.353913</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>4254.663683</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>4387.386702</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>4574.06268</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>4071.572595</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>4389.470668</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>4669.28555</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>4022.512014</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>4322.078593</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>4380.411803</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>4188.687904</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>4316.27752</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>4261.531381</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>4298.029258</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>4283.606426</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>4102.939004</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>4401.112416</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>4286.21903</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>4344.836133</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>4858.985267</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>4257.256474</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>4695.144762</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>4594.126832</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>4832.234449</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>4678.466386</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>4744.92647</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>5156.197382</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>5034.836423</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>4694.633717</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>5105.762624</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>5287.23124</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>4973.582058</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>4842.87751</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>5568.146543</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>4941.529365</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>4780.200856</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>5287.694024</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>4849.209903</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>5276.349014</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>5293.962434</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>4808.366395</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>4997.135176</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>4748.988745</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>5227.294591</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>4755.280559</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>4780.448948</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>5066.272496</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>4584.12584</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>4715.105124</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>4773.561771</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>4486.306201</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>5071.370474</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>4954.648027</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>4997.129746</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>4790.193043</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>5535.24068</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>4868.754703</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>4950.771141</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>5140.993509</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>4857.284294</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>5179.058352</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>5184.078017</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>5184.210627</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>5532.329663</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>5059.035579</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>5283.684949</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>5479.382657</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>5340.757195</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>5240.253036</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>5751.554354</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>5373.119417</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>5487.940796</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>4899.810718</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>5278.800746</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>5154.931027</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>5318.378293</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>5095.660842</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>4784.283436</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>5161.508337</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>4911.379333</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>5100.556888</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>4929.004213</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>5064.293204</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>4763.991451</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>4483.515888</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>5101.029554</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>5042.497776</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>4504.175702</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>4967.602205</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>5267.316332</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>4943.733094</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>4765.058344</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>5061.64852</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>5015.996855</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>4979.061696</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>4972.551038</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>5335.748731</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>4849.224977</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>5374.386974</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>5167.430107</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>5476.227433</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>5376.660071</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>5336.728256</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>5513.428517</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>5587.862592</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>5767.477283</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>5966.891232</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>5951.672573</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>5794.7309</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>6163.293696</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>5868.466849</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>5464.496527</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>6196.859549</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>5980.781227</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>5684.883293</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>6116.652269</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>6030.178104</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>5874.828498</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>5913.330953</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>6341.694287</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="488198923"/>
+        <c:axId val="561031466"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="488198923"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="561031466"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="561031466"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="488198923"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1000"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3416300" y="95250"/>
+        <a:ext cx="7536815" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3365500" y="2876550"/>
+        <a:ext cx="7537450" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>622300</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3365500" y="5664200"/>
+        <a:ext cx="7524750" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>18415</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3359150" y="8483600"/>
+        <a:ext cx="7555865" cy="5238750"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8470,5 +17859,6 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>